--- a/assets/.build/seo_meta_report.xlsx
+++ b/assets/.build/seo_meta_report.xlsx
@@ -428,10 +428,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -484,262 +484,548 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>directory/index.html</t>
+          <t>directory/bank/index.html</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>频道导航 - 正协导航</t>
+          <t>银行导航 - 正协导航</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>正协导航,频道导航,AI工具导航,政协专题导航,网站导航,垂类导航,精选收录</t>
+          <t>银行,商业银行,中央银行,政策性银行,网上银行,正协导航</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>正协导航频道中心：按垂类精选站点，AI 工具导航、政协专题导航一目了然，点击即可进入对应频道，正协导航 - 让每一次寻找，都不止于找到。</t>
+          <t>收录中央银行、政策性银行、国有商业银行及其他商业银行官网入口，覆盖国内主要银行机构，一键直达官方服务。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>directory/zhengxie/index.html</t>
+          <t>directory/gov/index.html</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>政协专题导航 - 正协导航</t>
+          <t>中国政府网站导航 - 正协导航</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>政协,政协委员,人民政协,协商民主,政协会议,各省市政协,民主党派,政务服务平台,正协导航,政协官网导航,AI工具,效率工具</t>
+          <t>中国政府,政府网站,政府官网,政务导航,中国政府网,国务院,部委,地方政府,政务服务平台,正协导航</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>收录全国政协及全国各省、市、区政协官网入口，为政协委员与办公人员提供一站式导航。</t>
+          <t>正协导航收录各级政府与政务服务平台：国务院及组成部门、各省市党委、人大、政府机构、民主党派等官方入口，权威可查、一键直达。正协导航 - 让每一次寻找，都不止于找到。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>index.html</t>
+          <t>directory/index.html</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>正协导航 - 让每一次寻找，都不止于找到</t>
+          <t>频道导航 - 正协导航</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>政协,政协委员,人民政协,协商民主,政协会议,各省市政协,民主党派,政务服务平台,正协导航,政协官网导航,AI工具,效率工具</t>
+          <t>正协导航,频道导航,AI工具导航,政协专题导航,网站导航,垂类导航,精选收录</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>专注政协与政务垂类，全量收录全国政协及各省市委官网、民主党派、政务服务平台与常用工具，为政协委员和政务工作者提供一站式入口。</t>
+          <t>正协导航频道导航：按垂类精选站点，AI 工具导航、政协专题导航一目了然，点击即可进入对应频道，正协导航 - 让每一次寻找，都不止于找到。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pages/about/index.html</t>
+          <t>directory/insurance/index.html</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>关于本站 - 正协导航</t>
+          <t>保险导航 - 正协导航</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>正协导航,关于本站,网址导航,网站导航</t>
+          <t>保险,保险公司,人寿保险,财险,正协导航</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>正协导航是一个全量收录的精选站点导航站，覆盖常用入口、AI智能、资讯媒体、设计创意、开发技术、学习教育、效率工具、影音娱乐等分类。</t>
+          <t>收录国内主要保险公司与保险平台官网入口，涵盖人寿、财险、健康险等领域，便于快速访问官方投保与理赔服务。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pages/changelog/index.html</t>
+          <t>directory/media/index.html</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>更新日志 - 正协导航</t>
+          <t>音视频媒体导航 - 正协导航</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>正协导航,更新日志,changelog,站点动态</t>
+          <t>直播,视频,短视频,音乐,音视频,正协导航</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>正协导航更新日志：记录站点分类、功能、页面与合规相关的迭代历史。</t>
+          <t>收录直播、长视频、短视频与音乐类主流平台，覆盖国内外音视频内容站点，方便一站式观看与收听。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pages/contact/index.html</t>
+          <t>directory/nav/index.html</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>联系我们 - 正协导航</t>
+          <t>导航网站大全 - 正协导航</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>正协导航,联系我们,收录申请,反馈,合作</t>
+          <t>导航网站,导航大全,网址导航,网站导航,导航站,综合导航,网址大全,垂直导航,工具导航,资源导航,正协导航</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>与正协导航取得联系：收录申请、死链反馈、内容纠错、合作咨询的统一入口。</t>
+          <t>正协导航收录各类型导航网站：综合导航、垂直导航、工具导航、资源导航等，精选分类、一键直达，帮你快速找到合适的导航站。正协导航 - 让每一次寻找，都不止于找到。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pages/disclaimer/index.html</t>
+          <t>directory/npc/index.html</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>免责声明 - 正协导航</t>
+          <t>全国人民代表大会导航 - 正协导航</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>正协导航,免责声明,网站导航声明</t>
+          <t>全国人民代表大会,全国人大,全国人大常委会,中国人大网,人大,国家立法机关,正协导航,人大导航</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>正协导航免责声明：说明本站收录性质、第三方内容责任边界、广告独立性、搜索结果来源及使用风险。</t>
+          <t>正协导航收录全国人民代表大会及其常务委员会官方入口：中国人大网权威可查、一键直达。正协导航 - 让每一次寻找，都不止于找到。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pages/guide/index.html</t>
+          <t>directory/party/index.html</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>使用指南 - 正协导航</t>
+          <t>中国共产党组织导航 - 正协导航</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>正协导航,使用指南,本地收藏,筛选,快捷键</t>
+          <t>中国共产党,党委,党组织,党建,党务,省委,市委,区委,共产党员网,正协导航,党组织导航</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>正协导航使用指南：本地收藏、三维度筛选、集合搜索、URL 分享、随机漫步与暗色模式等核心功能的使用方法。</t>
+          <t>正协导航收录中国共产党各级组织官方入口：中央及地方党委、党建门户，权威可查、一键直达。正协导航 - 让每一次寻找，都不止于找到。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pages/overview/index.html</t>
+          <t>directory/stock/index.html</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>网站全景 - 正协导航</t>
+          <t>证券导航 - 正协导航</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>正协导航,网站全景,站点中枢,全站总览,导航,榜单,博客</t>
+          <t>证券,券商,证券交易所,资管,正协导航</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>正协导航全站中枢：一页纵览导航产品、博客、榜单与各功能板块，看见全站架构与实时切片，从这里分发到任意板块。</t>
+          <t>收录证券公司、证券交易所与资产管理公司官网入口，覆盖证券开户、交易与研究服务，为投资者提供一站式导航。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pages/privacy/index.html</t>
+          <t>directory/world-bank/index.html</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>隐私政策 - 正协导航</t>
+          <t>外国银行导航 - 正协导航</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>正协导航,隐私政策,个人信息保护,导航网站隐私</t>
+          <t>外国银行,国际银行,跨境金融,正协导航</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>正协导航隐私政策：说明本站如何处理用户信息、使用的第三方统计与广告服务、Cookie 与本地存储、外链与跳转规则，以及您的权利。</t>
+          <t>收录全球主要国际银行与跨国银行集团官网入口，作为外国金融机构导航板块，便于跨境金融查询。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pages/sitemap/index.html</t>
+          <t>directory/world-gov/index.html</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>站点地图 - 正协导航</t>
+          <t>外国政府官网导航 - 正协导航</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>正协导航,站点地图,sitemap,分类索引</t>
+          <t>外国政府,政府官网,白宫,各国政府,美国白宫,英国政府,德国政府,法国政府,日本政府,政府门户,正协导航</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>正协导航站点地图：浏览全站分类索引（机构、政协、资讯媒体、常用入口、AI智能、设计创意、开发技术、学习教育、效率工具、影音娱乐）与所有子页面入口。</t>
+          <t>正协导航收录世界各国政府官方网站：美国白宫、英国、德国、法国、日本、韩国、印度、加拿大、澳大利亚等，总统府、政府门户、联邦机构一站直达。正协导航 - 让每一次寻找，都不止于找到。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>directory/world-insurance/index.html</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>外国保险导航 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>外国保险,国际保险,正协导航</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>收录全球主要国际保险集团官网入口，作为外国金融机构导航板块，便于跨国保险查询。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>directory/world-media/index.html</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>外国音视频媒体导航 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>外国媒体,流媒体,短视频,音乐,正协导航</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>收录全球主流流媒体、短视频、音乐与音频平台官网入口，作为外国媒体导航板块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>directory/world-stock/index.html</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>外国证券导航 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>外国证券,交易所,国际券商,正协导航</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>收录全球主要证券交易所与国际券商官网入口，作为外国金融导航板块，便于跨境投资查询。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>directory/zhengxie/index.html</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>政协专题导航 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>政协,政协委员,人民政协,协商民主,政协会议,各省市政协,民主党派,政务服务平台,正协导航,政协官网导航,AI工具,效率工具</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>收录全国政协及全国各省、市、区政协官网入口，并涵盖八个民主党派中央网站，为政协委员、民主党派成员与办公人员提供一站式导航。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>正协导航 - 让每一次寻找，都不止于找到</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>政协,政协委员,人民政协,协商民主,政协会议,各省市政协,民主党派,政务服务平台,正协导航,政协官网导航,AI工具,效率工具</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>专注政协与政务垂类，全量收录全国政协及各省市委官网、民主党派、政务服务平台与常用工具，为政协委员和政务工作者提供一站式入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pages/about/index.html</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>关于本站 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,关于本站,网址导航,网站导航</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>正协导航是一个全量收录的精选站点导航站，覆盖常用入口、AI智能、资讯媒体、设计创意、开发技术、学习教育、效率工具、影音娱乐等分类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pages/changelog/index.html</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>更新日志 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,更新日志,changelog,站点动态</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>正协导航更新日志：记录站点分类、功能、页面与合规相关的迭代历史。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pages/contact/index.html</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>联系我们 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,联系我们,收录申请,反馈,合作</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>与正协导航取得联系：收录申请、死链反馈、内容纠错、合作咨询的统一入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>pages/disclaimer/index.html</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>免责声明 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,免责声明,网站导航声明</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>正协导航免责声明：说明本站收录性质、第三方内容责任边界、广告独立性、搜索结果来源及使用风险。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pages/guide/index.html</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>使用指南 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,使用指南,本地收藏,筛选,快捷键</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>正协导航使用指南：本地收藏、三维度筛选、集合搜索、URL 分享、随机漫步与暗色模式等核心功能的使用方法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>pages/overview/index.html</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>网站全景 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,网站全景,站点中枢,全站总览,导航,榜单,博客</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>正协导航全站中枢：一页纵览导航产品、博客、榜单与各功能板块，看见全站架构与实时切片，从这里分发到任意板块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pages/privacy/index.html</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>隐私政策 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,隐私政策,个人信息保护,导航网站隐私</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>正协导航隐私政策：说明本站如何处理用户信息、使用的第三方统计与广告服务、Cookie 与本地存储、外链与跳转规则，以及您的权利。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pages/sitemap/index.html</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>站点地图 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>正协导航,站点地图,sitemap,分类索引</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>正协导航站点地图：浏览全站分类索引（机构、政协、资讯媒体、常用入口、AI智能、设计创意、开发技术、学习教育、效率工具、影音娱乐）与所有子页面入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>pages/submit/index.html</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>收录申请 - 正协导航</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>正协导航,收录申请,网站收录,网址提交</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>提交你的站点到正协导航。我们收录优质的网站，覆盖AI智能、资讯媒体、设计创意、开发技术、学习教育、效率工具、影音娱乐等领域。</t>
         </is>
